--- a/导出模板.xlsx
+++ b/导出模板.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>编号</t>
   </si>
@@ -55,9 +55,6 @@
   </si>
   <si>
     <t>合计</t>
-  </si>
-  <si>
-    <t>班次</t>
   </si>
   <si>
     <t>日期</t>
@@ -278,7 +275,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="38">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -293,18 +290,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2DCDB"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCE6F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCCFFFF"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -502,7 +487,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -666,82 +651,6 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -879,7 +788,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="20">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="14">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
@@ -891,120 +800,120 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="21">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="23">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="24">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="23">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="25">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="18">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="17">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="19">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1035,9 +944,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1059,12 +965,6 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1086,67 +986,34 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="3" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1161,61 +1028,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="13" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="2" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="2" borderId="10" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="19" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="13" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1530,10 +1346,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:BG13"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5"/>
+  <dimension ref="A1:P8"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <sheetData>
-    <row r="1" spans="1:59">
+    <row r="1" spans="1:16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1568,839 +1384,164 @@
       <c r="N1" s="8"/>
       <c r="O1" s="8"/>
       <c r="P1" s="9"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="8"/>
-      <c r="S1" s="8"/>
-      <c r="T1" s="8"/>
-      <c r="U1" s="8"/>
-      <c r="V1" s="8"/>
-      <c r="W1" s="9"/>
-      <c r="X1" s="7"/>
-      <c r="Y1" s="8"/>
-      <c r="Z1" s="8"/>
-      <c r="AA1" s="8"/>
-      <c r="AB1" s="8"/>
-      <c r="AC1" s="8"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="7"/>
-      <c r="AF1" s="8"/>
-      <c r="AG1" s="8"/>
-      <c r="AH1" s="8"/>
-      <c r="AI1" s="8"/>
-      <c r="AJ1" s="8"/>
-      <c r="AK1" s="9"/>
-      <c r="AL1" s="7"/>
-      <c r="AM1" s="8"/>
-      <c r="AN1" s="8"/>
-      <c r="AO1" s="8"/>
-      <c r="AP1" s="8"/>
-      <c r="AQ1" s="8"/>
-      <c r="AR1" s="9"/>
-      <c r="AS1" s="7"/>
-      <c r="AT1" s="8"/>
-      <c r="AU1" s="8"/>
-      <c r="AV1" s="8"/>
-      <c r="AW1" s="8"/>
-      <c r="AX1" s="8"/>
-      <c r="AY1" s="9"/>
-      <c r="AZ1" s="7"/>
-      <c r="BA1" s="8"/>
-      <c r="BB1" s="8"/>
-      <c r="BC1" s="8"/>
-      <c r="BD1" s="8"/>
-      <c r="BE1" s="8"/>
-      <c r="BF1" s="9"/>
-      <c r="BG1" s="10" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="10"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14" t="s">
         <v>9</v>
       </c>
+      <c r="I2" s="15"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
     </row>
-    <row r="2" spans="1:59">
-      <c r="A2" s="11"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="15" t="s">
+    <row r="3" ht="14.25" spans="1:16">
+      <c r="A3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="18"/>
-      <c r="P2" s="18"/>
-      <c r="Q2" s="17"/>
-      <c r="R2" s="17"/>
-      <c r="S2" s="17"/>
-      <c r="T2" s="17"/>
-      <c r="U2" s="17"/>
-      <c r="V2" s="18"/>
-      <c r="W2" s="18"/>
-      <c r="X2" s="17"/>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="17"/>
-      <c r="AA2" s="17"/>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="17"/>
-      <c r="AD2" s="18"/>
-      <c r="AE2" s="18"/>
-      <c r="AF2" s="18"/>
-      <c r="AG2" s="17"/>
-      <c r="AH2" s="17"/>
-      <c r="AI2" s="17"/>
-      <c r="AJ2" s="18"/>
-      <c r="AK2" s="18"/>
-      <c r="AL2" s="17"/>
-      <c r="AM2" s="17"/>
-      <c r="AN2" s="17"/>
-      <c r="AO2" s="17"/>
-      <c r="AP2" s="17"/>
-      <c r="AQ2" s="18"/>
-      <c r="AR2" s="17"/>
-      <c r="AS2" s="17"/>
-      <c r="AT2" s="18"/>
-      <c r="AU2" s="18"/>
-      <c r="AV2" s="18"/>
-      <c r="AW2" s="18"/>
-      <c r="AX2" s="18"/>
-      <c r="AY2" s="18"/>
-      <c r="AZ2" s="18"/>
-      <c r="BA2" s="17"/>
-      <c r="BB2" s="17"/>
-      <c r="BC2" s="17"/>
-      <c r="BD2" s="17"/>
-      <c r="BE2" s="17"/>
-      <c r="BF2" s="18"/>
-      <c r="BG2" s="19"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
     </row>
-    <row r="3" ht="14.25" spans="1:59">
-      <c r="A3" s="20"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="26"/>
-      <c r="Y3" s="26"/>
-      <c r="Z3" s="26"/>
-      <c r="AA3" s="26"/>
-      <c r="AB3" s="26"/>
-      <c r="AC3" s="26"/>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="27"/>
-      <c r="AG3" s="26"/>
-      <c r="AH3" s="26"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="27"/>
-      <c r="AK3" s="27"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="26"/>
-      <c r="AN3" s="26"/>
-      <c r="AO3" s="26"/>
-      <c r="AP3" s="26"/>
-      <c r="AQ3" s="27"/>
-      <c r="AR3" s="26"/>
-      <c r="AS3" s="26"/>
-      <c r="AT3" s="27"/>
-      <c r="AU3" s="27"/>
-      <c r="AV3" s="27"/>
-      <c r="AW3" s="27"/>
-      <c r="AX3" s="27"/>
-      <c r="AY3" s="27"/>
-      <c r="AZ3" s="27"/>
-      <c r="BA3" s="26"/>
-      <c r="BB3" s="26"/>
-      <c r="BC3" s="26"/>
-      <c r="BD3" s="26"/>
-      <c r="BE3" s="26"/>
-      <c r="BF3" s="27"/>
-      <c r="BG3" s="28"/>
-    </row>
-    <row r="4" spans="1:59">
-      <c r="A4" s="29"/>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="32"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="34" t="s">
+    <row r="5" spans="1:16">
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="I4" s="35"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
-      <c r="L4" s="36"/>
-      <c r="M4" s="36"/>
-      <c r="N4" s="36"/>
-      <c r="O4" s="36"/>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="36"/>
-      <c r="U4" s="36"/>
-      <c r="V4" s="36"/>
-      <c r="W4" s="36"/>
-      <c r="X4" s="36"/>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="36"/>
-      <c r="AA4" s="36"/>
-      <c r="AB4" s="36"/>
-      <c r="AC4" s="36"/>
-      <c r="AD4" s="36"/>
-      <c r="AE4" s="36"/>
-      <c r="AF4" s="36"/>
-      <c r="AG4" s="36"/>
-      <c r="AH4" s="36"/>
-      <c r="AI4" s="36"/>
-      <c r="AJ4" s="36"/>
-      <c r="AK4" s="36"/>
-      <c r="AL4" s="36"/>
-      <c r="AM4" s="36"/>
-      <c r="AN4" s="36"/>
-      <c r="AO4" s="36"/>
-      <c r="AP4" s="36"/>
-      <c r="AQ4" s="36"/>
-      <c r="AR4" s="36"/>
-      <c r="AS4" s="36"/>
-      <c r="AT4" s="36"/>
-      <c r="AU4" s="36"/>
-      <c r="AV4" s="36"/>
-      <c r="AW4" s="36"/>
-      <c r="AX4" s="36"/>
-      <c r="AY4" s="36"/>
-      <c r="AZ4" s="36"/>
-      <c r="BA4" s="36"/>
-      <c r="BB4" s="36"/>
-      <c r="BC4" s="36"/>
-      <c r="BD4" s="36"/>
-      <c r="BE4" s="36"/>
-      <c r="BF4" s="36"/>
-      <c r="BG4" s="37"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
     </row>
-    <row r="5" spans="1:59">
-      <c r="A5" s="38"/>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="43" t="s">
+    <row r="6" spans="1:16">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="44"/>
-      <c r="J5" s="45"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="45"/>
-      <c r="M5" s="45"/>
-      <c r="N5" s="45"/>
-      <c r="O5" s="45"/>
-      <c r="P5" s="45"/>
-      <c r="Q5" s="45"/>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45"/>
-      <c r="T5" s="45"/>
-      <c r="U5" s="45"/>
-      <c r="V5" s="45"/>
-      <c r="W5" s="45"/>
-      <c r="X5" s="45"/>
-      <c r="Y5" s="45"/>
-      <c r="Z5" s="45"/>
-      <c r="AA5" s="45"/>
-      <c r="AB5" s="45"/>
-      <c r="AC5" s="45"/>
-      <c r="AD5" s="45"/>
-      <c r="AE5" s="45"/>
-      <c r="AF5" s="45"/>
-      <c r="AG5" s="45"/>
-      <c r="AH5" s="45"/>
-      <c r="AI5" s="45"/>
-      <c r="AJ5" s="45"/>
-      <c r="AK5" s="45"/>
-      <c r="AL5" s="45"/>
-      <c r="AM5" s="45"/>
-      <c r="AN5" s="45"/>
-      <c r="AO5" s="45"/>
-      <c r="AP5" s="45"/>
-      <c r="AQ5" s="45"/>
-      <c r="AR5" s="45"/>
-      <c r="AS5" s="45"/>
-      <c r="AT5" s="45"/>
-      <c r="AU5" s="45"/>
-      <c r="AV5" s="45"/>
-      <c r="AW5" s="45"/>
-      <c r="AX5" s="45"/>
-      <c r="AY5" s="45"/>
-      <c r="AZ5" s="45"/>
-      <c r="BA5" s="45"/>
-      <c r="BB5" s="45"/>
-      <c r="BC5" s="45"/>
-      <c r="BD5" s="45"/>
-      <c r="BE5" s="45"/>
-      <c r="BF5" s="45"/>
-      <c r="BG5" s="46"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
     </row>
-    <row r="6" spans="1:59">
-      <c r="A6" s="38"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="41"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="47" t="s">
+    <row r="7" spans="1:16">
+      <c r="A7" s="28"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28"/>
+      <c r="H7" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="I6" s="46"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="48"/>
-      <c r="P6" s="48"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="48"/>
-      <c r="V6" s="48"/>
-      <c r="W6" s="48"/>
-      <c r="X6" s="48"/>
-      <c r="Y6" s="48"/>
-      <c r="Z6" s="48"/>
-      <c r="AA6" s="48"/>
-      <c r="AB6" s="48"/>
-      <c r="AC6" s="48"/>
-      <c r="AD6" s="48"/>
-      <c r="AE6" s="48"/>
-      <c r="AF6" s="48"/>
-      <c r="AG6" s="48"/>
-      <c r="AH6" s="48"/>
-      <c r="AI6" s="48"/>
-      <c r="AJ6" s="48"/>
-      <c r="AK6" s="48"/>
-      <c r="AL6" s="48"/>
-      <c r="AM6" s="48"/>
-      <c r="AN6" s="48"/>
-      <c r="AO6" s="48"/>
-      <c r="AP6" s="48"/>
-      <c r="AQ6" s="48"/>
-      <c r="AR6" s="48"/>
-      <c r="AS6" s="48"/>
-      <c r="AT6" s="48"/>
-      <c r="AU6" s="48"/>
-      <c r="AV6" s="48"/>
-      <c r="AW6" s="48"/>
-      <c r="AX6" s="48"/>
-      <c r="AY6" s="48"/>
-      <c r="AZ6" s="48"/>
-      <c r="BA6" s="48"/>
-      <c r="BB6" s="48"/>
-      <c r="BC6" s="48"/>
-      <c r="BD6" s="48"/>
-      <c r="BE6" s="48"/>
-      <c r="BF6" s="48"/>
-      <c r="BG6" s="46"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37"/>
+      <c r="N7" s="37"/>
+      <c r="O7" s="37"/>
+      <c r="P7" s="37"/>
     </row>
-    <row r="7" spans="1:59">
-      <c r="A7" s="38"/>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="49" t="s">
+    <row r="8" ht="14.25" spans="1:16">
+      <c r="A8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="50"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
-      <c r="Z7" s="51"/>
-      <c r="AA7" s="51"/>
-      <c r="AB7" s="51"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="51"/>
-      <c r="AE7" s="51"/>
-      <c r="AF7" s="51"/>
-      <c r="AG7" s="51"/>
-      <c r="AH7" s="51"/>
-      <c r="AI7" s="51"/>
-      <c r="AJ7" s="51"/>
-      <c r="AK7" s="51"/>
-      <c r="AL7" s="51"/>
-      <c r="AM7" s="51"/>
-      <c r="AN7" s="51"/>
-      <c r="AO7" s="51"/>
-      <c r="AP7" s="51"/>
-      <c r="AQ7" s="51"/>
-      <c r="AR7" s="51"/>
-      <c r="AS7" s="51"/>
-      <c r="AT7" s="51"/>
-      <c r="AU7" s="51"/>
-      <c r="AV7" s="51"/>
-      <c r="AW7" s="51"/>
-      <c r="AX7" s="51"/>
-      <c r="AY7" s="51"/>
-      <c r="AZ7" s="51"/>
-      <c r="BA7" s="51"/>
-      <c r="BB7" s="51"/>
-      <c r="BC7" s="51"/>
-      <c r="BD7" s="51"/>
-      <c r="BE7" s="51"/>
-      <c r="BF7" s="51"/>
-      <c r="BG7" s="48"/>
-    </row>
-    <row r="8" ht="14.25" spans="1:59">
-      <c r="A8" s="38"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="54"/>
-      <c r="J8" s="54"/>
-      <c r="K8" s="54"/>
-      <c r="L8" s="54"/>
-      <c r="M8" s="54"/>
-      <c r="N8" s="54"/>
-      <c r="O8" s="54"/>
-      <c r="P8" s="54"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="54"/>
-      <c r="S8" s="54"/>
-      <c r="T8" s="54"/>
-      <c r="U8" s="54"/>
-      <c r="V8" s="54"/>
-      <c r="W8" s="54"/>
-      <c r="X8" s="54"/>
-      <c r="Y8" s="54"/>
-      <c r="Z8" s="54"/>
-      <c r="AA8" s="54"/>
-      <c r="AB8" s="54"/>
-      <c r="AC8" s="54"/>
-      <c r="AD8" s="54"/>
-      <c r="AE8" s="54"/>
-      <c r="AF8" s="54"/>
-      <c r="AG8" s="54"/>
-      <c r="AH8" s="54"/>
-      <c r="AI8" s="54"/>
-      <c r="AJ8" s="54"/>
-      <c r="AK8" s="54"/>
-      <c r="AL8" s="54"/>
-      <c r="AM8" s="54"/>
-      <c r="AN8" s="54"/>
-      <c r="AO8" s="54"/>
-      <c r="AP8" s="54"/>
-      <c r="AQ8" s="54"/>
-      <c r="AR8" s="54"/>
-      <c r="AS8" s="54"/>
-      <c r="AT8" s="54"/>
-      <c r="AU8" s="54"/>
-      <c r="AV8" s="54"/>
-      <c r="AW8" s="54"/>
-      <c r="AX8" s="54"/>
-      <c r="AY8" s="54"/>
-      <c r="AZ8" s="54"/>
-      <c r="BA8" s="54"/>
-      <c r="BB8" s="54"/>
-      <c r="BC8" s="54"/>
-      <c r="BD8" s="54"/>
-      <c r="BE8" s="54"/>
-      <c r="BF8" s="54"/>
-      <c r="BG8" s="48"/>
-    </row>
-    <row r="9" spans="1:59">
-      <c r="A9" s="55"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="56"/>
-      <c r="D9" s="57"/>
-      <c r="E9" s="57"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="36"/>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="36"/>
-      <c r="R9" s="36"/>
-      <c r="S9" s="36"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="36"/>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="36"/>
-      <c r="Z9" s="36"/>
-      <c r="AA9" s="36"/>
-      <c r="AB9" s="36"/>
-      <c r="AC9" s="36"/>
-      <c r="AD9" s="36"/>
-      <c r="AE9" s="36"/>
-      <c r="AF9" s="36"/>
-      <c r="AG9" s="36"/>
-      <c r="AH9" s="36"/>
-      <c r="AI9" s="36"/>
-      <c r="AJ9" s="36"/>
-      <c r="AK9" s="36"/>
-      <c r="AL9" s="36"/>
-      <c r="AM9" s="36"/>
-      <c r="AN9" s="36"/>
-      <c r="AO9" s="36"/>
-      <c r="AP9" s="36"/>
-      <c r="AQ9" s="36"/>
-      <c r="AR9" s="36"/>
-      <c r="AS9" s="36"/>
-      <c r="AT9" s="36"/>
-      <c r="AU9" s="36"/>
-      <c r="AV9" s="36"/>
-      <c r="AW9" s="36"/>
-      <c r="AX9" s="36"/>
-      <c r="AY9" s="36"/>
-      <c r="AZ9" s="36"/>
-      <c r="BA9" s="36"/>
-      <c r="BB9" s="36"/>
-      <c r="BC9" s="36"/>
-      <c r="BD9" s="36"/>
-      <c r="BE9" s="36"/>
-      <c r="BF9" s="36"/>
-      <c r="BG9" s="58"/>
-    </row>
-    <row r="10" spans="1:59">
-      <c r="A10" s="59"/>
-      <c r="B10" s="60"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="61"/>
-      <c r="H10" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="44"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="45"/>
-      <c r="M10" s="45"/>
-      <c r="N10" s="45"/>
-      <c r="O10" s="45"/>
-      <c r="P10" s="45"/>
-      <c r="Q10" s="45"/>
-      <c r="R10" s="45"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="45"/>
-      <c r="W10" s="45"/>
-      <c r="X10" s="45"/>
-      <c r="Y10" s="45"/>
-      <c r="Z10" s="45"/>
-      <c r="AA10" s="45"/>
-      <c r="AB10" s="45"/>
-      <c r="AC10" s="45"/>
-      <c r="AD10" s="45"/>
-      <c r="AE10" s="45"/>
-      <c r="AF10" s="45"/>
-      <c r="AG10" s="45"/>
-      <c r="AH10" s="45"/>
-      <c r="AI10" s="45"/>
-      <c r="AJ10" s="45"/>
-      <c r="AK10" s="45"/>
-      <c r="AL10" s="45"/>
-      <c r="AM10" s="45"/>
-      <c r="AN10" s="45"/>
-      <c r="AO10" s="45"/>
-      <c r="AP10" s="45"/>
-      <c r="AQ10" s="45"/>
-      <c r="AR10" s="45"/>
-      <c r="AS10" s="45"/>
-      <c r="AT10" s="45"/>
-      <c r="AU10" s="45"/>
-      <c r="AV10" s="45"/>
-      <c r="AW10" s="45"/>
-      <c r="AX10" s="45"/>
-      <c r="AY10" s="45"/>
-      <c r="AZ10" s="45"/>
-      <c r="BA10" s="45"/>
-      <c r="BB10" s="45"/>
-      <c r="BC10" s="45"/>
-      <c r="BD10" s="45"/>
-      <c r="BE10" s="45"/>
-      <c r="BF10" s="45"/>
-      <c r="BG10" s="62"/>
-    </row>
-    <row r="11" spans="1:59">
-      <c r="A11" s="59"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="I11" s="62"/>
-      <c r="J11" s="63"/>
-      <c r="K11" s="63"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="63"/>
-      <c r="N11" s="63"/>
-      <c r="O11" s="63"/>
-      <c r="P11" s="63"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="63"/>
-      <c r="S11" s="63"/>
-      <c r="T11" s="63"/>
-      <c r="U11" s="63"/>
-      <c r="V11" s="63"/>
-      <c r="W11" s="63"/>
-      <c r="X11" s="63"/>
-      <c r="Y11" s="63"/>
-      <c r="Z11" s="63"/>
-      <c r="AA11" s="63"/>
-      <c r="AB11" s="63"/>
-      <c r="AC11" s="63"/>
-      <c r="AD11" s="63"/>
-      <c r="AE11" s="63"/>
-      <c r="AF11" s="63"/>
-      <c r="AG11" s="63"/>
-      <c r="AH11" s="63"/>
-      <c r="AI11" s="63"/>
-      <c r="AJ11" s="63"/>
-      <c r="AK11" s="63"/>
-      <c r="AL11" s="63"/>
-      <c r="AM11" s="63"/>
-      <c r="AN11" s="64"/>
-      <c r="AO11" s="63"/>
-      <c r="AP11" s="63"/>
-      <c r="AQ11" s="63"/>
-      <c r="AR11" s="63"/>
-      <c r="AS11" s="63"/>
-      <c r="AT11" s="63"/>
-      <c r="AU11" s="63"/>
-      <c r="AV11" s="63"/>
-      <c r="AW11" s="63"/>
-      <c r="AX11" s="63"/>
-      <c r="AY11" s="63"/>
-      <c r="AZ11" s="63"/>
-      <c r="BA11" s="63"/>
-      <c r="BB11" s="63"/>
-      <c r="BC11" s="63"/>
-      <c r="BD11" s="63"/>
-      <c r="BE11" s="63"/>
-      <c r="BF11" s="63"/>
-      <c r="BG11" s="63"/>
-    </row>
-    <row r="12" spans="1:59">
-      <c r="A12" s="59"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="61"/>
-      <c r="H12" s="65" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="66"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="66"/>
-      <c r="L12" s="66"/>
-      <c r="M12" s="66"/>
-      <c r="N12" s="66"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="66"/>
-      <c r="S12" s="66"/>
-      <c r="T12" s="66"/>
-      <c r="U12" s="66"/>
-      <c r="V12" s="66"/>
-      <c r="W12" s="66"/>
-      <c r="X12" s="66"/>
-      <c r="Y12" s="66"/>
-      <c r="Z12" s="66"/>
-      <c r="AA12" s="66"/>
-      <c r="AB12" s="66"/>
-      <c r="AC12" s="66"/>
-      <c r="AD12" s="66"/>
-      <c r="AE12" s="66"/>
-      <c r="AF12" s="66"/>
-      <c r="AG12" s="66"/>
-      <c r="AH12" s="66"/>
-      <c r="AI12" s="66"/>
-      <c r="AJ12" s="66"/>
-      <c r="AK12" s="66"/>
-      <c r="AL12" s="66"/>
-      <c r="AM12" s="66"/>
-      <c r="AN12" s="66"/>
-      <c r="AO12" s="66"/>
-      <c r="AP12" s="66"/>
-      <c r="AQ12" s="66"/>
-      <c r="AR12" s="66"/>
-      <c r="AS12" s="66"/>
-      <c r="AT12" s="66"/>
-      <c r="AU12" s="66"/>
-      <c r="AV12" s="66"/>
-      <c r="AW12" s="66"/>
-      <c r="AX12" s="66"/>
-      <c r="AY12" s="66"/>
-      <c r="AZ12" s="66"/>
-      <c r="BA12" s="66"/>
-      <c r="BB12" s="66"/>
-      <c r="BC12" s="66"/>
-      <c r="BD12" s="66"/>
-      <c r="BE12" s="66"/>
-      <c r="BF12" s="66"/>
-      <c r="BG12" s="67"/>
-    </row>
-    <row r="13" ht="14.25" spans="1:59">
-      <c r="A13" s="68"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="70"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="54" t="s">
-        <v>15</v>
-      </c>
-      <c r="I13" s="54"/>
-      <c r="J13" s="54"/>
-      <c r="K13" s="54"/>
-      <c r="L13" s="54"/>
-      <c r="M13" s="54"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="54"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="54"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="54"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="54"/>
-      <c r="V13" s="54"/>
-      <c r="W13" s="54"/>
-      <c r="X13" s="54"/>
-      <c r="Y13" s="54"/>
-      <c r="Z13" s="54"/>
-      <c r="AA13" s="54"/>
-      <c r="AB13" s="54"/>
-      <c r="AC13" s="54"/>
-      <c r="AD13" s="54"/>
-      <c r="AE13" s="54"/>
-      <c r="AF13" s="54"/>
-      <c r="AG13" s="54"/>
-      <c r="AH13" s="54"/>
-      <c r="AI13" s="54"/>
-      <c r="AJ13" s="54"/>
-      <c r="AK13" s="54"/>
-      <c r="AL13" s="54"/>
-      <c r="AM13" s="54"/>
-      <c r="AN13" s="54"/>
-      <c r="AO13" s="54"/>
-      <c r="AP13" s="54"/>
-      <c r="AQ13" s="54"/>
-      <c r="AR13" s="54"/>
-      <c r="AS13" s="54"/>
-      <c r="AT13" s="54"/>
-      <c r="AU13" s="54"/>
-      <c r="AV13" s="54"/>
-      <c r="AW13" s="54"/>
-      <c r="AX13" s="54"/>
-      <c r="AY13" s="54"/>
-      <c r="AZ13" s="54"/>
-      <c r="BA13" s="54"/>
-      <c r="BB13" s="54"/>
-      <c r="BC13" s="54"/>
-      <c r="BD13" s="54"/>
-      <c r="BE13" s="54"/>
-      <c r="BF13" s="54"/>
-      <c r="BG13" s="48"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="39"/>
+      <c r="P8" s="39"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="17">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="Q1:W1"/>
-    <mergeCell ref="X1:AD1"/>
-    <mergeCell ref="AE1:AK1"/>
-    <mergeCell ref="AL1:AR1"/>
-    <mergeCell ref="AS1:AY1"/>
-    <mergeCell ref="AZ1:BF1"/>
     <mergeCell ref="A1:A3"/>
     <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A9:A13"/>
     <mergeCell ref="B1:B3"/>
     <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B9:B13"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="C4:C8"/>
-    <mergeCell ref="C9:C13"/>
     <mergeCell ref="D1:D2"/>
     <mergeCell ref="D4:D8"/>
-    <mergeCell ref="D9:D13"/>
     <mergeCell ref="E1:E3"/>
     <mergeCell ref="E4:E8"/>
-    <mergeCell ref="E9:E13"/>
     <mergeCell ref="F1:F3"/>
     <mergeCell ref="F4:F8"/>
-    <mergeCell ref="F9:F13"/>
     <mergeCell ref="G1:G3"/>
     <mergeCell ref="G4:G8"/>
-    <mergeCell ref="G9:G13"/>
     <mergeCell ref="H2:H3"/>
     <mergeCell ref="I1:I3"/>
-    <mergeCell ref="BG1:BG3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
